--- a/InputData/elec/RLYr/RLYr Reliability Lookahead Years.xlsx
+++ b/InputData/elec/RLYr/RLYr Reliability Lookahead Years.xlsx
@@ -1,50 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RLYr\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30EAE77-B42C-4E39-BD5D-4D7A277947B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RLYr" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="About" sheetId="1" r:id="rId1"/>
+    <sheet name="RLYr" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>RLYr Reliability Lookahead Years</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>Clean-firm project lead times (interconnection + development + construction)</t>
+  </si>
+  <si>
+    <t>LBNL; NREL ATB; industry reporting</t>
+  </si>
+  <si>
+    <t>LBNL Queued Up interconnection-queue reports; NREL Annual Technology Baseline; industry lead-time estimates</t>
+  </si>
+  <si>
+    <t>https://emp.lbl.gov/queues</t>
+  </si>
+  <si>
+    <t>Utility resource-planning practice (forward procurement horizons)</t>
+  </si>
+  <si>
+    <t>CPUC; state IRP filings</t>
+  </si>
+  <si>
+    <t>CPUC Decision D.21-06-035 (mid-term reliability procurement); utility IRP action plans</t>
+  </si>
+  <si>
+    <t>https://docs.cpuc.ca.gov/PublishedDocs/Published/G000/M389/K603/389603637.PDF</t>
+  </si>
+  <si>
+    <t>IRP action plans commit resources 5-10 years out; CPUC's 2021 mid-term reliability order procured 11.5 GW roughly 7 years ahead; utilities facing statutory deadlines (IL CEJA, WA CETA, MN/Xcel) file procurement plans most of a decade before compliance dates. VERIFY AGAINST PRIMARY SOURCES BEFORE EXTERNAL USE.</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>What this input does</t>
+  </si>
+  <si>
+    <t>Foresight window (years) for the electricity reliability mechanism. It sets (1) how far ahead the capacity market's five-year-style reliability check looks (This Year Flag for Five Year Reliability Check), and (2) the span and divisor of the non-qualifying reliability credit rampdown's forward average (policy and BAU twins). It is a planning horizon - how far ahead markets and planners act on a foreseeable capacity need - not a capacity-market auction tenor.</t>
+  </si>
+  <si>
+    <t>Maximum value</t>
+  </si>
+  <si>
+    <t>Must not exceed the number of Future Year subscript elements (77 as of model version 4.0.6: 2025-2100 in InputData/plcy-schd/FY/FY.csv). Values beyond FINAL TIME are capped in-model by MIN(Time + RLYr, FINAL TIME) for the reliability check; the rampdown window simply extends past the schedule's last defined year, where the requirement holds at its final value.</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>reliability lookahead years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approximate lead times for the resources the reliability mechanism procures at the margin: geothermal ~7-10 yrs; nuclear/SMR ~8-12; gas-CCS ~6-8; new gas CC ~5-7 (turbine backlog); hydrogen turbines ~5-7. Wind/solar ~3-5 yrs incl. queues (LBNL median queue duration ~5 yrs), but wind/solar are not the marginal firm reliability resource. </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,93 +136,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -435,204 +451,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RLYr Reliability Lookahead Years</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Sources:</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Clean-firm project lead times (interconnection + development + construction)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>LBNL; NREL ATB; industry reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>LBNL Queued Up interconnection-queue reports; NREL Annual Technology Baseline; industry lead-time estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>https://emp.lbl.gov/queues</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Approximate lead times for the resources the reliability mechanism procures at the margin: geothermal ~7-10 yrs; nuclear/SMR ~8-12; gas-CCS ~6-8; new gas CC ~5-7 (turbine backlog); hydrogen turbines ~5-7. Wind/solar ~3-5 yrs incl. queues (LBNL median queue duration ~5 yrs), but wind/solar are not the marginal firm reliability resource. FIGURES ARE FROM WORKING KNOWLEDGE - VERIFY AGAINST THE PRIMARY SOURCES BEFORE EXTERNAL USE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Utility resource-planning practice (forward procurement horizons)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>CPUC; state IRP filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>CPUC Decision D.21-06-035 (mid-term reliability procurement); utility IRP action plans</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>https://docs.cpuc.ca.gov/PublishedDocs/Published/G000/M389/K603/389603637.PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IRP action plans commit resources 5-10 years out; CPUC's 2021 mid-term reliability order procured 11.5 GW roughly 7 years ahead; utilities facing statutory deadlines (IL CEJA, WA CETA, MN/Xcel) file procurement plans most of a decade before compliance dates. VERIFY AGAINST PRIMARY SOURCES BEFORE EXTERNAL USE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>What this input does</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Foresight window (years) for the electricity reliability mechanism. It sets (1) how far ahead the capacity market's five-year-style reliability check looks (This Year Flag for Five Year Reliability Check), and (2) the span and divisor of the non-qualifying reliability credit rampdown's forward average (policy and BAU twins). It is a planning horizon - how far ahead markets and planners act on a foreseeable capacity need - not a capacity-market auction tenor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Choice of default (5 years; 8 years evaluated and not yet adopted)</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>The default preserves the model's long-standing 5-year window. A longer window (8 years) was proposed to match the lead time of the MARGINAL FIRM entrant the mechanism procures (clean-dispatchable: ~7-10 yrs) rather than wind/solar lead times (~3-5 yrs), and an IL BAU test on the 2026-08-25 model showed it softening the CEJA statutory-cliff capacity-price spike. However, the 2026-08-25 seven-state validation sweep on eps-us c5883191 failed the adoption gates: 8 years raised cumulative capacity-market costs in ME/NM/AR (ME BAU capacity payments persist through 2050 instead of ending after the statute binds - suspected interaction with the keep-online retirement stock), raised peak prices in MN and some CA runs, and moved material VRE volume between the CES/RPS cost-effectiveness channel and the reliability channel (the channel-shift regression the validation was designed to catch). See LOOKAHEAD_VALIDATION_2026-08-25.md in the model repo before revisiting the default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Maximum value</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Must not exceed the number of Future Year subscript elements (77 as of model version 4.0.6: 2025-2100 in InputData/plcy-schd/FY/FY.csv). Values beyond FINAL TIME are capped in-model by MIN(Time + RLYr, FINAL TIME) for the reliability check; the rampdown window simply extends past the schedule's last defined year, where the requirement holds at its final value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Backward compatibility</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Setting this input to 5 reproduces the prior hard-coded behavior exactly (verified bit-identical on national BAU and IL BAU at the refactor, 2026-08-25).</t>
-        </is>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId2"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>reliability lookahead years</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
